--- a/models/hpp/data/datosPais.xlsx
+++ b/models/hpp/data/datosPais.xlsx
@@ -9,20 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13128" windowHeight="6108"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13128" windowHeight="6108" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="countries" sheetId="2" r:id="rId2"/>
+    <sheet name="template" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$122</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="55">
   <si>
     <t>pais</t>
   </si>
@@ -148,13 +150,55 @@
   </si>
   <si>
     <t>Compra Directa 223/2025</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Alpha2</t>
+  </si>
+  <si>
+    <t>ar</t>
+  </si>
+  <si>
+    <t>br</t>
+  </si>
+  <si>
+    <t>co</t>
+  </si>
+  <si>
+    <t>cl</t>
+  </si>
+  <si>
+    <t>cr</t>
+  </si>
+  <si>
+    <t>jm</t>
+  </si>
+  <si>
+    <t>mx</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>uy</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>bo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -165,6 +209,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -196,11 +256,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Incorrecto" xfId="1" builtinId="27"/>
@@ -498,7 +560,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F122"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
@@ -735,7 +798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -755,7 +818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -775,7 +838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -795,7 +858,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -815,7 +878,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -835,7 +898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -855,7 +918,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -875,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -895,7 +958,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -915,7 +978,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -935,7 +998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -946,7 +1009,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -966,7 +1029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -986,7 +1049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -1006,7 +1069,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1026,7 +1089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1046,7 +1109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1066,7 +1129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1086,7 +1149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1106,7 +1169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1126,7 +1189,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -1146,7 +1209,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1157,7 +1220,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1177,7 +1240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1197,7 +1260,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1217,7 +1280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1237,7 +1300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1257,7 +1320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1340,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -1297,7 +1360,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1317,7 +1380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -1337,7 +1400,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1357,7 +1420,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1368,7 +1431,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1388,7 +1451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1408,7 +1471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1428,7 +1491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -1448,7 +1511,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1468,7 +1531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1488,7 +1551,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1508,7 +1571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1528,7 +1591,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1548,7 +1611,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1568,7 +1631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1579,7 +1642,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -1599,7 +1662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1619,7 +1682,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -1639,7 +1702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1659,7 +1722,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -1679,7 +1742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -1699,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -1719,7 +1782,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -1739,7 +1802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -1759,7 +1822,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -1779,7 +1842,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -1790,7 +1853,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -1810,7 +1873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -1830,7 +1893,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -1850,7 +1913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -1870,7 +1933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -1890,7 +1953,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>20</v>
       </c>
@@ -1910,7 +1973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -1930,7 +1993,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>20</v>
       </c>
@@ -1950,7 +2013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -1970,7 +2033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>20</v>
       </c>
@@ -1990,7 +2053,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -2001,7 +2064,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -2021,7 +2084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -2041,7 +2104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -2061,7 +2124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -2081,7 +2144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -2101,7 +2164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -2121,7 +2184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -2141,7 +2204,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -2161,7 +2224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -2181,7 +2244,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -2201,7 +2264,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -2212,7 +2275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -2232,7 +2295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -2252,7 +2315,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -2272,7 +2335,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -2292,7 +2355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>31</v>
       </c>
@@ -2312,7 +2375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>31</v>
       </c>
@@ -2332,7 +2395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>31</v>
       </c>
@@ -2352,7 +2415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>33</v>
       </c>
@@ -2372,7 +2435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -2392,7 +2455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -2412,7 +2475,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -2432,7 +2495,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -2452,7 +2515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -2472,7 +2535,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -2492,7 +2555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -2512,7 +2575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>35</v>
       </c>
@@ -2532,7 +2595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>35</v>
       </c>
@@ -2552,7 +2615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>35</v>
       </c>
@@ -2572,7 +2635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>35</v>
       </c>
@@ -2592,7 +2655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>35</v>
       </c>
@@ -2612,7 +2675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>35</v>
       </c>
@@ -2632,7 +2695,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>31</v>
       </c>
@@ -2652,7 +2715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>31</v>
       </c>
@@ -2672,7 +2735,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>31</v>
       </c>
@@ -2692,7 +2755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -2712,7 +2775,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>33</v>
       </c>
@@ -2732,7 +2795,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>33</v>
       </c>
@@ -2752,7 +2815,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>35</v>
       </c>
@@ -2772,7 +2835,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>35</v>
       </c>
@@ -2792,7 +2855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>35</v>
       </c>
@@ -2812,7 +2875,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>31</v>
       </c>
@@ -2823,7 +2886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>33</v>
       </c>
@@ -2834,7 +2897,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>35</v>
       </c>
@@ -2845,8 +2908,488 @@
         <v>12</v>
       </c>
     </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>53</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123">
+        <v>508067</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>53</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>53</v>
+      </c>
+      <c r="B126" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126">
+        <v>0.71099999999999997</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>53</v>
+      </c>
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127">
+        <v>33.229999999999997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>53</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129">
+        <v>81.400000000000006</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>53</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130">
+        <v>62.04</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>53</v>
+      </c>
+      <c r="B131" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131">
+        <v>790.49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>53</v>
+      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132">
+        <v>2.97</v>
+      </c>
+      <c r="D132" s="4"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>53</v>
+      </c>
+      <c r="B133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F122">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Argentina"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>508067</v>
+      </c>
+      <c r="D2">
+        <v>2025</v>
+      </c>
+      <c r="E2">
+        <v>2025</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>29.2</v>
+      </c>
+      <c r="D3">
+        <v>2024</v>
+      </c>
+      <c r="E3">
+        <v>2025</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0.995</v>
+      </c>
+      <c r="D4">
+        <v>2023</v>
+      </c>
+      <c r="E4">
+        <v>2025</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="D5">
+        <v>2013</v>
+      </c>
+      <c r="E5">
+        <v>2023</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>33.229999999999997</v>
+      </c>
+      <c r="D6">
+        <v>2023</v>
+      </c>
+      <c r="E6">
+        <v>2025</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>0.1</v>
+      </c>
+      <c r="D7">
+        <v>2024</v>
+      </c>
+      <c r="E7">
+        <v>2025</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="D8">
+        <v>2023</v>
+      </c>
+      <c r="E8">
+        <v>2025</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>62.04</v>
+      </c>
+      <c r="D9">
+        <v>45108</v>
+      </c>
+      <c r="E9">
+        <v>45108</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>790.49</v>
+      </c>
+      <c r="D10">
+        <v>45108</v>
+      </c>
+      <c r="E10">
+        <v>45108</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>2.97</v>
+      </c>
+      <c r="D11">
+        <v>45108</v>
+      </c>
+      <c r="E11">
+        <v>45108</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/models/hpp/data/datosPais.xlsx
+++ b/models/hpp/data/datosPais.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13128" windowHeight="6108" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13128" windowHeight="6108"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -560,7 +560,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -798,7 +797,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -818,7 +817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -838,7 +837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -858,7 +857,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -878,7 +877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -898,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -918,7 +917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -938,7 +937,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -958,7 +957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -978,7 +977,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -998,7 +997,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1009,7 +1008,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1029,7 +1028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1089,7 +1088,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1129,7 +1128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1149,7 +1148,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1168,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1189,7 +1188,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -1209,7 +1208,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1220,7 +1219,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1260,7 +1259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1280,7 +1279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1320,7 +1319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -1340,7 +1339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -1360,7 +1359,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1420,7 +1419,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -1431,7 +1430,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -1451,7 +1450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1471,7 +1470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1491,7 +1490,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -1511,7 +1510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -1531,7 +1530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -1551,7 +1550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1571,7 +1570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -1611,7 +1610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -1662,7 +1661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -1682,7 +1681,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -1702,7 +1701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -1722,7 +1721,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -1742,7 +1741,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -1762,7 +1761,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -1782,7 +1781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -1842,7 +1841,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -1853,7 +1852,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -1893,7 +1892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>20</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>20</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>20</v>
       </c>
@@ -1973,7 +1972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>20</v>
       </c>
@@ -1993,7 +1992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>20</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>20</v>
       </c>
@@ -2053,7 +2052,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -2064,7 +2063,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -2084,7 +2083,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -2124,7 +2123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -2144,7 +2143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -2184,7 +2183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -2244,7 +2243,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>21</v>
       </c>
@@ -2264,7 +2263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>21</v>
       </c>
@@ -2275,7 +2274,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -2295,7 +2294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -2315,7 +2314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -2335,7 +2334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>31</v>
       </c>
@@ -2355,7 +2354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>31</v>
       </c>
@@ -2375,7 +2374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>31</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>31</v>
       </c>
@@ -2415,7 +2414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>33</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -2455,7 +2454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -2475,7 +2474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -2495,7 +2494,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -2535,7 +2534,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>35</v>
       </c>
@@ -2575,7 +2574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>35</v>
       </c>
@@ -2595,7 +2594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>35</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>35</v>
       </c>
@@ -2635,7 +2634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>35</v>
       </c>
@@ -2655,7 +2654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>35</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>35</v>
       </c>
@@ -2695,7 +2694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>31</v>
       </c>
@@ -2715,7 +2714,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>31</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>31</v>
       </c>
@@ -2755,7 +2754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>33</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>33</v>
       </c>
@@ -2795,7 +2794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>33</v>
       </c>
@@ -2815,7 +2814,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>35</v>
       </c>
@@ -2835,7 +2834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>35</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>35</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>31</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>33</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>35</v>
       </c>
@@ -3031,13 +3030,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F122">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Argentina"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
